--- a/JsonConverter/ExcelFiles/InspectObject.xlsx
+++ b/JsonConverter/ExcelFiles/InspectObject.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30121"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA92FA22-3B95-4225-8543-5A77B02322AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEFE382B-AC11-427D-A7F4-3A3CF7A05F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>조사 오브젝트 고유 ID</t>
   </si>
@@ -48,6 +48,15 @@
     <t>처음 출력할 조사 텍스트 ID</t>
   </si>
   <si>
+    <t>보상 enumType</t>
+  </si>
+  <si>
+    <t>조사 완료 후 출력할 문장</t>
+  </si>
+  <si>
+    <t>아이콘 경로</t>
+  </si>
+  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -69,19 +78,70 @@
     <t>StartInspectTextId</t>
   </si>
   <si>
-    <t>inspect_test_note</t>
-  </si>
-  <si>
-    <t>피가 묻은 노트</t>
-  </si>
-  <si>
-    <t>뭔가가 적혀 있는 노트이다. 조사해보자.</t>
-  </si>
-  <si>
-    <t>Prefabs/InspectObjects/Object_Note</t>
-  </si>
-  <si>
-    <t>inspect_note_start</t>
+    <t>CompleteRewardType</t>
+  </si>
+  <si>
+    <t>CompleteInspectDescription</t>
+  </si>
+  <si>
+    <t>IconPath</t>
+  </si>
+  <si>
+    <t>inspectobject_brokenframe</t>
+  </si>
+  <si>
+    <t>깨진 액자</t>
+  </si>
+  <si>
+    <t>선임 연구원들의 단체 사진이다.
+그 사건이 일어나기 전까진 분위기가 좋았던 듯하다.</t>
+  </si>
+  <si>
+    <t>Prefabs/InspectObjects/Object_BrokenFrame</t>
+  </si>
+  <si>
+    <t>inspect_brokenframe_start</t>
+  </si>
+  <si>
+    <t>Icons/Icon_BrokenFrame</t>
+  </si>
+  <si>
+    <t>inspectobject_mapprint</t>
+  </si>
+  <si>
+    <t>연구소 지도</t>
+  </si>
+  <si>
+    <t>Prefabs/InspectObjects/Object_MapPrint</t>
+  </si>
+  <si>
+    <t>inspect_mapprint_start</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>연구소의 구조를 자세히 확인했다.
+이제 M키를 눌러 미니맵을 볼 수 있다.</t>
+  </si>
+  <si>
+    <t>inspectobject_idcard</t>
+  </si>
+  <si>
+    <t>ID카드</t>
+  </si>
+  <si>
+    <t>수석 연구원에게 지급하는 ID카드다.
+이 카드로 연구소 대부분의 시설에 출입 수 있다.</t>
+  </si>
+  <si>
+    <t>Prefabs/InspectObjects/Object_IDCard</t>
+  </si>
+  <si>
+    <t>inspect_idcard_start</t>
+  </si>
+  <si>
+    <t>Icons/Icon_IDCard</t>
   </si>
 </sst>
 </file>
@@ -152,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -160,6 +220,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -329,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -337,9 +400,13 @@
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="42.5" customWidth="1"/>
     <col min="5" max="5" width="37.5" customWidth="1"/>
+    <col min="6" max="6" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -355,56 +422,126 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8" ht="14.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.5">
+    <row r="4" spans="1:8" ht="33.75">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="66.75">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="33.75">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
